--- a/Result/profitability/2729.xlsx
+++ b/Result/profitability/2729.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM64"/>
+  <dimension ref="A1:AM65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,10 +669,10 @@
         <v>7.38</v>
       </c>
       <c r="M2" t="n">
-        <v>2.56375</v>
+        <v>2.43125</v>
       </c>
       <c r="N2" t="n">
-        <v>51.31125</v>
+        <v>51.16125</v>
       </c>
       <c r="O2" t="n">
         <v>1</v>
@@ -780,10 +780,10 @@
         <v>7.09</v>
       </c>
       <c r="M3" t="n">
-        <v>3.08875</v>
+        <v>3.13625</v>
       </c>
       <c r="N3" t="n">
-        <v>51.63875</v>
+        <v>51.7075</v>
       </c>
       <c r="O3" t="n">
         <v>1</v>
@@ -8558,6 +8558,133 @@
         <v>115.1</v>
       </c>
     </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>2729</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>1636</v>
+      </c>
+      <c r="D65" t="n">
+        <v>801</v>
+      </c>
+      <c r="E65" t="n">
+        <v>836</v>
+      </c>
+      <c r="F65" t="n">
+        <v>51.08</v>
+      </c>
+      <c r="G65" t="n">
+        <v>118</v>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>7.24%</t>
+        </is>
+      </c>
+      <c r="I65" t="n">
+        <v>-12</v>
+      </c>
+      <c r="J65" t="n">
+        <v>107</v>
+      </c>
+      <c r="K65" t="n">
+        <v>78</v>
+      </c>
+      <c r="L65" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="M65" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="N65" t="n">
+        <v>50.85625</v>
+      </c>
+      <c r="O65" t="n">
+        <v>1</v>
+      </c>
+      <c r="P65" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q65" t="n">
+        <v>0</v>
+      </c>
+      <c r="R65" t="n">
+        <v>0</v>
+      </c>
+      <c r="S65" t="n">
+        <v>1</v>
+      </c>
+      <c r="T65" t="n">
+        <v>0</v>
+      </c>
+      <c r="U65" t="n">
+        <v>1</v>
+      </c>
+      <c r="V65" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W65" t="n">
+        <v>0.1900000000000002</v>
+      </c>
+      <c r="X65" t="n">
+        <v>0.1158536585365855</v>
+      </c>
+      <c r="Y65" t="n">
+        <v>1.640000000000001</v>
+      </c>
+      <c r="Z65" t="n">
+        <v>0.03317152103559873</v>
+      </c>
+      <c r="AA65" t="n">
+        <v>-0.07999999999999985</v>
+      </c>
+      <c r="AB65" t="n">
+        <v>-0.04188481675392663</v>
+      </c>
+      <c r="AC65" t="n">
+        <v>-0.3200000000000003</v>
+      </c>
+      <c r="AD65" t="n">
+        <v>-0.006225680933852118</v>
+      </c>
+      <c r="AE65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="n">
+        <v>1</v>
+      </c>
+      <c r="AH65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AI65" t="n">
+        <v>0</v>
+      </c>
+      <c r="AJ65" t="inlineStr">
+        <is>
+          <t>EPS衰退 / 毛利率衰退</t>
+        </is>
+      </c>
+      <c r="AK65" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL65" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM65" t="n">
+        <v>115.2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
